--- a/r4-core-102-Krankenanstaltennummer-identifier-is-missing-R4-HL7®-AT-Core-Organization-Profile/StructureDefinition-at-core-ext-patient-religion.xlsx
+++ b/r4-core-102-Krankenanstaltennummer-identifier-is-missing-R4-HL7®-AT-Core-Organization-Profile/StructureDefinition-at-core-ext-patient-religion.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="134">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-22T14:29:33+00:00</t>
+    <t>2024-10-30T16:15:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -133,7 +133,10 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:Element</t>
+    <t>element:Patient</t>
+  </si>
+  <si>
+    <t>element:http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient#Patient</t>
   </si>
   <si>
     <t>ID</t>
@@ -558,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -733,6 +736,14 @@
       </c>
       <c r="B22" t="s" s="2">
         <v>39</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -785,115 +796,115 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2">
@@ -909,10 +920,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>21</v>
@@ -924,7 +935,7 @@
         <v>21</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L2" t="s" s="2">
         <v>9</v>
@@ -984,16 +995,16 @@
         <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>21</v>
@@ -1001,10 +1012,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1012,10 +1023,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>21</v>
@@ -1027,13 +1038,13 @@
         <v>21</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1084,13 +1095,13 @@
         <v>21</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>21</v>
@@ -1099,26 +1110,26 @@
         <v>21</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>21</v>
@@ -1130,16 +1141,16 @@
         <v>21</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
@@ -1177,55 +1188,55 @@
         <v>21</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>21</v>
@@ -1237,13 +1248,13 @@
         <v>21</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1294,19 +1305,19 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>21</v>
@@ -1314,10 +1325,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1325,10 +1336,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>21</v>
@@ -1340,13 +1351,13 @@
         <v>21</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1397,13 +1408,13 @@
         <v>21</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>21</v>
@@ -1412,15 +1423,15 @@
         <v>21</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1428,10 +1439,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>21</v>
@@ -1443,13 +1454,13 @@
         <v>21</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>31</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1488,31 +1499,31 @@
         <v>21</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AD7" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>21</v>
@@ -1520,10 +1531,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1531,10 +1542,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>21</v>
@@ -1546,16 +1557,16 @@
         <v>21</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1563,7 +1574,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>21</v>
@@ -1605,13 +1616,13 @@
         <v>21</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>21</v>
@@ -1620,15 +1631,15 @@
         <v>21</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1636,10 +1647,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
@@ -1651,13 +1662,13 @@
         <v>21</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1684,11 +1695,11 @@
         <v>21</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Y9" s="2"/>
       <c r="Z9" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>21</v>
@@ -1706,43 +1717,43 @@
         <v>21</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>21</v>
@@ -1754,13 +1765,13 @@
         <v>21</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1811,19 +1822,19 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
@@ -1831,10 +1842,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1842,10 +1853,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -1857,13 +1868,13 @@
         <v>21</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1914,13 +1925,13 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>21</v>
@@ -1929,15 +1940,15 @@
         <v>21</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1945,10 +1956,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>21</v>
@@ -1960,13 +1971,13 @@
         <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>31</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2005,31 +2016,31 @@
         <v>21</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>21</v>
@@ -2037,10 +2048,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2048,10 +2059,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
@@ -2063,16 +2074,16 @@
         <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2080,7 +2091,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>21</v>
@@ -2122,13 +2133,13 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>21</v>
@@ -2137,15 +2148,15 @@
         <v>21</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2153,10 +2164,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>21</v>
@@ -2168,13 +2179,13 @@
         <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2225,30 +2236,30 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2256,10 +2267,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>21</v>
@@ -2271,16 +2282,16 @@
         <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2330,13 +2341,13 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>21</v>
@@ -2345,15 +2356,15 @@
         <v>21</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2361,10 +2372,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>21</v>
@@ -2376,13 +2387,13 @@
         <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2433,22 +2444,22 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
